--- a/bore_search_tool/power_automate/MGA_master_register.xlsx
+++ b/bore_search_tool/power_automate/MGA_master_register.xlsx
@@ -148,8 +148,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MGAData" displayName="MGAData" ref="A1:U2" headerRowCount="1">
-  <autoFilter ref="A1:U2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MGAData" displayName="MGAData" ref="A1:V2" headerRowCount="1">
+  <autoFilter ref="A1:V2"/>
   <tableColumns count="21">
     <tableColumn id="1" name="Tenure Holder"/>
     <tableColumn id="2" name="RN"/>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -517,7 +517,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Sheet Tenure holders: the access codes the flow checks. Give each company its code privately. To rotate a code, change AccessCode in this sheet; the flow reads it on every submission. Set Active to No to suspend a company.</t>
+          <t>Sheet Tenure holders: the access codes the flow checks. Give each company its code privately. To rotate a code, change AccessCode in this sheet; the flow reads it on every submission. Set Active to No to suspend a company. EmailDomain must never be blank: the flow refuses a company whose domain is blank.</t>
         </is>
       </c>
     </row>
@@ -535,6 +535,20 @@
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Annual reports must not include any monetary amounts paid, or proposed to be paid, to the bore owner. The tool blocks amounts in comments; check the Comments column on review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Emailed reports: when the page cannot reach the flow it emails the report to OGIA.UWIR with the row attached as an Excel file. Flow B files it automatically when the email carries the coded block and the sender's domain matches; otherwise the email is flagged and OGIA pastes the attached row into MGA data (Source = Manual, copy ClientRef from the file).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Duplicates: the ClientRef column identifies one version of a report. If a row with the same ClientRef already exists, the flows answer with the existing Submission ID instead of adding a row.</t>
         </is>
       </c>
     </row>
@@ -549,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:V2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -573,6 +587,7 @@
     <col width="22" customWidth="1" min="19" max="19"/>
     <col width="10" customWidth="1" min="20" max="20"/>
     <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="18" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -681,6 +696,11 @@
           <t>App version</t>
         </is>
       </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>ClientRef</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -716,16 +736,11 @@
           <t>In negotiations</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
           <t>Example row copied from the template: delete it once real submissions arrive.</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>2022-23</t>
@@ -746,14 +761,16 @@
           <t>example@company.com.au</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr">
         <is>
           <t>Example</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>EXAMPLE</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -870,7 +887,6 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -898,7 +914,6 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -926,7 +941,6 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -942,7 +956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -994,7 +1008,6 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
@@ -1054,7 +1067,6 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
       <c r="B11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
@@ -1150,7 +1162,6 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
       <c r="B20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
@@ -1258,7 +1269,6 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
       <c r="B30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
@@ -1314,6 +1324,97 @@
       <c r="B35" s="4" t="inlineStr">
         <is>
           <t>The bore is decommissioned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Register columns (added by OGIA, after the template columns)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Submission ID</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>MGA-yyyymmdd-XXXXXX when lodged through the Bore Search Tool (Brisbane date); EMAIL-&lt;ClientRef&gt; when lodged by email. Quoted on the receipt the officer receives.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Submitted at</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Brisbane time the flow filed the row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Submitted by / Submitter name</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Work email (checked against EmailDomain) and the name typed by the officer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Replaces submission</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Submission ID of the earlier version when a company amends a report. Keep the latest per bore and period.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Bore Search Tool (flow A), Email (flow B) or Manual (typed in by OGIA).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>App version</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Version of the page that produced the row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ClientRef</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>The page's reference for one version of a report. The flows look it up before adding a row, so a retry after a timeout or an email sent twice never produces a second row. Fill it in when entering an emailed row by hand (it is in the attached file).</t>
         </is>
       </c>
     </row>

--- a/bore_search_tool/power_automate/MGA_master_register.xlsx
+++ b/bore_search_tool/power_automate/MGA_master_register.xlsx
@@ -149,8 +149,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MGAData" displayName="MGAData" ref="A1:V2" headerRowCount="1">
-  <autoFilter ref="A1:V2"/>
-  <tableColumns count="21">
+  <tableColumns count="22">
     <tableColumn id="1" name="Tenure Holder"/>
     <tableColumn id="2" name="RN"/>
     <tableColumn id="3" name="Bore assessment status"/>
@@ -172,6 +171,7 @@
     <tableColumn id="19" name="Replaces submission"/>
     <tableColumn id="20" name="Source"/>
     <tableColumn id="21" name="App version"/>
+    <tableColumn id="22" name="ClientRef"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -517,7 +517,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Sheet Tenure holders: the access codes the flow checks. Give each company its code privately. To rotate a code, change AccessCode in this sheet; the flow reads it on every submission. Set Active to No to suspend a company. EmailDomain must never be blank: the flow refuses a company whose domain is blank.</t>
+          <t>Sheet Tenure holders: the access codes the flow checks. The AccessCode column ships with placeholders: replace each one with a code of your own (for example three groups of four letters and digits) before the first submission; never publish the codes. Give each company its code privately. To rotate a code, change AccessCode in this sheet; the flow reads it on every submission. Set Active to No to suspend a company. EmailDomain must never be blank: the flow refuses a company whose domain is blank.</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ARW-QVIK-J9VB</t>
+          <t>SET-BY-OGIA-ARROW</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ORG-YUB2-5R2X</t>
+          <t>SET-BY-OGIA-ORIGIN</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SAN-FXLD-N0G3</t>
+          <t>SET-BY-OGIA-SANTOS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>QGC-86MB-7V8U</t>
+          <t>SET-BY-OGIA-QGC</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">

--- a/bore_search_tool/power_automate/MGA_master_register.xlsx
+++ b/bore_search_tool/power_automate/MGA_master_register.xlsx
@@ -178,8 +178,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TenureHolders" displayName="TenureHolders" ref="A1:F5" headerRowCount="1">
-  <autoFilter ref="A1:F5"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TenureHolders" displayName="TenureHolders" ref="A1:F11" headerRowCount="1">
+  <autoFilter ref="A1:F11"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Code"/>
     <tableColumn id="2" name="HolderName"/>
@@ -786,7 +786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -939,6 +939,174 @@
       <c r="E5" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SENEX</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Senex Energy</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SET-BY-OGIA-SENEX</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Not yet onboarded: fill AccessCode and EmailDomain, then set Active to Yes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AGL</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>AGL</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SET-BY-OGIA-AGL</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Not yet onboarded: fill AccessCode and EmailDomain, then set Active to Yes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ADZ ENERGY</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ADZ Energy</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SET-BY-OGIA-ADZ-ENERGY</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Not yet onboarded: fill AccessCode and EmailDomain, then set Active to Yes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BRIDGEPORT ENERGY</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Bridgeport Energy</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SET-BY-OGIA-BRIDGEPORT-ENERGY</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Not yet onboarded: fill AccessCode and EmailDomain, then set Active to Yes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DENISON GAS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Denison Gas</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SET-BY-OGIA-DENISON-GAS</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Not yet onboarded: fill AccessCode and EmailDomain, then set Active to Yes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>OGT</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>OGT</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SET-BY-OGIA-OGT</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Not yet onboarded: fill AccessCode and EmailDomain, then set Active to Yes.</t>
         </is>
       </c>
     </row>
